--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N104_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.40090790026825</v>
+        <v>9.00264753379359</v>
       </c>
       <c r="D2" t="n">
-        <v>56.35748619305159</v>
+        <v>9.158091506370884</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F2" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>85.56979810265247</v>
+        <v>13.90509219168103</v>
       </c>
       <c r="D3" t="n">
-        <v>80.19270613065194</v>
+        <v>13.03131474623094</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F3" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.32359467434213</v>
+        <v>8.177584134580597</v>
       </c>
       <c r="D4" t="n">
-        <v>25.93169590304625</v>
+        <v>4.213900584245017</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F4" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.88223113184672</v>
+        <v>7.293362558925091</v>
       </c>
       <c r="D5" t="n">
-        <v>40.5467785403477</v>
+        <v>6.5888515128065</v>
       </c>
       <c r="E5" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F5" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.25401861351457</v>
+        <v>10.92877802469612</v>
       </c>
       <c r="D6" t="n">
-        <v>63.03659147310529</v>
+        <v>10.24344611437961</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F6" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.93825914117897</v>
+        <v>6.327467110441582</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9496473315243</v>
+        <v>2.591817691372698</v>
       </c>
       <c r="E7" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F7" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.60991115976268</v>
+        <v>7.249110563461436</v>
       </c>
       <c r="D8" t="n">
-        <v>39.41642929399888</v>
+        <v>6.405169760274818</v>
       </c>
       <c r="E8" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F8" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>67.81199145772449</v>
+        <v>11.01944861188023</v>
       </c>
       <c r="D9" t="n">
-        <v>59.58675493101376</v>
+        <v>9.682847676289736</v>
       </c>
       <c r="E9" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F9" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.84347477768037</v>
+        <v>5.66206465137306</v>
       </c>
       <c r="D10" t="n">
-        <v>30.12167576656365</v>
+        <v>4.894772312066594</v>
       </c>
       <c r="E10" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F10" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.6545316933051</v>
+        <v>5.631361400162079</v>
       </c>
       <c r="D11" t="n">
-        <v>11.16183866332951</v>
+        <v>1.813798782791045</v>
       </c>
       <c r="E11" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F11" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.28553594633822</v>
+        <v>7.846399591279961</v>
       </c>
       <c r="D12" t="n">
-        <v>36.21616641739035</v>
+        <v>5.885127042825933</v>
       </c>
       <c r="E12" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F12" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.90941833318796</v>
+        <v>9.085280479143044</v>
       </c>
       <c r="D13" t="n">
-        <v>51.80305675674365</v>
+        <v>8.417996722970843</v>
       </c>
       <c r="E13" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F13" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.2125986254368</v>
+        <v>7.18454727663348</v>
       </c>
       <c r="D14" t="n">
-        <v>44.18314114533867</v>
+        <v>7.179760436117535</v>
       </c>
       <c r="E14" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F14" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.23164641977093</v>
+        <v>8.162642543212776</v>
       </c>
       <c r="D15" t="n">
-        <v>50.24751560748848</v>
+        <v>8.165221286216878</v>
       </c>
       <c r="E15" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F15" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.96981840611049</v>
+        <v>6.495095490992955</v>
       </c>
       <c r="D16" t="n">
-        <v>40.00079158973673</v>
+        <v>6.500128633332219</v>
       </c>
       <c r="E16" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F16" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.117822275973863</v>
+        <v>1.319146119845753</v>
       </c>
       <c r="D17" t="n">
-        <v>8.333040587283564</v>
+        <v>1.354119095433579</v>
       </c>
       <c r="E17" t="n">
-        <v>16.63183536418615</v>
+        <v>2.702673246680249</v>
       </c>
       <c r="F17" t="n">
-        <v>18.99305467906126</v>
+        <v>3.086371385347455</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
